--- a/docs/叙世者·录入模板.xlsx
+++ b/docs/叙世者·录入模板.xlsx
@@ -12,6 +12,7 @@
     <sheet name="故事" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="场地" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="伙伴" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="词表" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -69,7 +70,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +90,56 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF7DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B5CF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4A95A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E9D2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E6F5E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006E87A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B04A5A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D98868"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8B87D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003E5C6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9A8B4"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -141,6 +192,19 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -820,7 +884,7 @@
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -850,7 +914,7 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>年份 *</t>
+          <t>婚期 *</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
@@ -932,17 +996,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>婚礼 / 纪念日 / 宝宝宴 / 其他</t>
+          <t>下拉选择</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>如 2026</t>
+          <t>精确日期,如 2026-10-03;未定档期至少填年份,如 2026</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>春夏秋冬</t>
+          <t>下拉选择(填了精确婚期可留空)</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -967,7 +1031,7 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>逗号分隔,如:星空, 自然野趣</t>
+          <t>从「词表」页挑,逗号分隔可多个,如:星空, 自然野趣;词表没有的新词先加进词表</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -982,7 +1046,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>已成篇 / 进行中</t>
+          <t>下拉选择</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
@@ -1022,8 +1086,10 @@
           <t>婚礼</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
-        <v>2026</v>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
@@ -1321,6 +1387,17 @@
       <c r="Q15" s="7" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="B4:B15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效输入" error="请从下拉列表中选择" type="list">
+      <formula1>"婚礼,纪念日,宝宝宴,求婚,其他"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D4:D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效输入" error="请从下拉列表中选择" type="list">
+      <formula1>"春,夏,秋,冬"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L4:L15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效输入" error="请从下拉列表中选择" type="list">
+      <formula1>"已成篇,进行中"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1331,14 +1408,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1354,15 +1432,20 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
+          <t>场地类型 *</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
           <t>一句话简介</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>我们的设计沉淀</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>照片素材位置</t>
         </is>
@@ -1381,15 +1464,20 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
+          <t>下拉选择(也是搜索维度)</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
           <t>这个场地的气质,一句话。会公开</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>我们在这里做过什么、探索出什么。会公开</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>写清放在哪里</t>
         </is>
@@ -1408,15 +1496,20 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
+          <t>教堂/礼堂</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
           <t>(示例)一座临河的老教堂。</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>(示例)我们在此做过三场仪式,沉淀了……</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>网盘/场地/新天安堂</t>
         </is>
@@ -1428,6 +1521,7 @@
       <c r="C4" s="7" t="n"/>
       <c r="D4" s="7" t="n"/>
       <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -1435,6 +1529,7 @@
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
@@ -1442,6 +1537,7 @@
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
@@ -1449,6 +1545,7 @@
       <c r="C7" s="7" t="n"/>
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
@@ -1456,6 +1553,7 @@
       <c r="C8" s="7" t="n"/>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -1463,6 +1561,7 @@
       <c r="C9" s="7" t="n"/>
       <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -1470,6 +1569,7 @@
       <c r="C10" s="7" t="n"/>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -1477,6 +1577,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
@@ -1484,6 +1585,7 @@
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -1491,6 +1593,7 @@
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -1498,6 +1601,7 @@
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -1505,8 +1609,14 @@
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C4:C15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效输入" error="请从下拉列表中选择" type="list">
+      <formula1>"酒店,教堂/礼堂,户外/山野,庭园/宅院,艺术空间,餐厅,其他"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1667,4 +1777,271 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>风格词表(可自行增改;故事表的风格标签从这里挑)</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>元素词示例(自由填写,不限于此)</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>配色参考</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>填色号或直接写色名都可以;渲染前会统一归一化到站点色板,气质不会跑偏</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>星空</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>星石</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>暮紫</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>#8B5CF6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>自然野趣</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>手写信</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>暖金</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>#D4A95A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>山野</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>老照片</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>米白</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>#F3E9D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>庭园</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>干花</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>松绿</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>#2E6F5E</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>教堂古典</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>胶片放映</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>雾蓝</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>#6E87A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>现代极简</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>黑胶</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>绯红</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>#B04A5A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>复古胶片</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>外婆的桌布</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>珊瑚</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>#D98868</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>东方雅致</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>一棵树</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>杏子</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>#E8B87D</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>热烈浓彩</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>黛青</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>#3E5C6B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>清透浅色</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>藕粉</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>#D9A8B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>书信手作</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>音乐现场</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>